--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_49.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_49.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6692424.274189235</v>
+        <v>6732361.452964313</v>
       </c>
     </row>
     <row r="7">
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>481.9993129555745</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>449.4745782429939</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E2" t="n">
         <v>4.363289606868648</v>
@@ -672,19 +672,19 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>408.0096587035274</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>97.12488247690055</v>
+        <v>97.12488247690067</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>514.0207012252074</v>
       </c>
       <c r="M2" t="n">
         <v>814</v>
@@ -693,25 +693,25 @@
         <v>194.5855355810472</v>
       </c>
       <c r="O2" t="n">
-        <v>522.1267819420524</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q2" t="n">
-        <v>797.8013999999999</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>93.56939138541452</v>
       </c>
       <c r="S2" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U2" t="n">
-        <v>341.8309294230461</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -720,7 +720,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>192.2818334606677</v>
+        <v>592.2818334606677</v>
       </c>
       <c r="Y2" t="n">
         <v>111.3174326828064</v>
@@ -733,25 +733,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>167.115840263807</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>133.5328253992193</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
-        <v>141.9749974174577</v>
+        <v>141.974997417455</v>
       </c>
       <c r="O4" t="n">
         <v>240.445564079015</v>
@@ -897,7 +897,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E5" t="n">
         <v>4.363289606868648</v>
@@ -906,46 +906,46 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.75737228701621</v>
+        <v>347.245603989746</v>
       </c>
       <c r="H5" t="n">
-        <v>100.6192915779623</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>797.8013999999999</v>
+        <v>418.7382696589336</v>
       </c>
       <c r="K5" t="n">
-        <v>97.1248824769005</v>
+        <v>97.12488247690067</v>
       </c>
       <c r="L5" t="n">
-        <v>814.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>814</v>
       </c>
       <c r="N5" t="n">
-        <v>194.5855355810472</v>
+        <v>814</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>708.6062368062544</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>505.9281819420526</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U5" t="n">
         <v>649.2212965486107</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1018,19 +1018,19 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>547.2737972923793</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>5.357765217513816</v>
+        <v>130.9153024145154</v>
       </c>
       <c r="U6" t="n">
-        <v>400.2103597601867</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>72.23629157494297</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617061042</v>
       </c>
       <c r="N7" t="n">
         <v>171.1850752716849</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>320.9396782847063</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>425.4875446583047</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1137,16 +1137,16 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>4.363289606868648</v>
+        <v>347.8515213095984</v>
       </c>
       <c r="F8" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G8" t="n">
         <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -1155,25 +1155,25 @@
         <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
+        <v>97.12488247690067</v>
+      </c>
+      <c r="L8" t="n">
+        <v>281.7754478641663</v>
+      </c>
+      <c r="M8" t="n">
         <v>814</v>
       </c>
-      <c r="L8" t="n">
-        <v>313.1545016101269</v>
-      </c>
-      <c r="M8" t="n">
-        <v>297.9910820919849</v>
-      </c>
       <c r="N8" t="n">
-        <v>194.5855355810472</v>
+        <v>814</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>370.9706110579117</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U8" t="n">
         <v>649.2212965486107</v>
       </c>
       <c r="V8" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
@@ -1210,13 +1210,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>153.9536147159909</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1252,16 +1252,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>547.2737972923793</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>290.0041245104569</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>114.9691617061046</v>
+        <v>114.9691617061031</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
@@ -1368,19 +1368,19 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>165.5148171418603</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
         <v>183.0096587035274</v>
@@ -1416,7 +1416,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>141.1382265029168</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
@@ -1431,10 +1431,10 @@
         <v>413.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>367.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1565,13 +1565,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1614,10 +1614,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>67.57968198731129</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>157.0096587035274</v>
@@ -1805,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>52.97841917455702</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>52.97841917455702</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>125.4590200934258</v>
+        <v>125.8896287080119</v>
       </c>
       <c r="G17" t="n">
         <v>124.7573722870162</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>215.8481678023229</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T17" t="n">
         <v>307.6755817285639</v>
@@ -2006,7 +2006,7 @@
         <v>6.53621805555548</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2024,16 +2024,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2042,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>240.6152697053352</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>83.37347970285543</v>
+        <v>73.25953106976573</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="20">
@@ -2234,16 +2234,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1.387730005009886</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2264,28 +2264,28 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>339.4016293563777</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="23">
@@ -2501,25 +2501,25 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>107.8765809499618</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>233.4184877263874</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>189.411675845388</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,10 +2601,10 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
         <v>424.2212965486107</v>
@@ -2619,7 +2619,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2717,13 +2717,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>22.7015426558702</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H28" t="n">
         <v>3.77112610161862</v>
@@ -2741,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>127.3785421071857</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -2790,22 +2790,22 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>189.411675845388</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>74.93013737369456</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,13 +2844,13 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>404.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>413.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>367.2818334606677</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>48.91631418759635</v>
       </c>
     </row>
     <row r="32">
@@ -3048,19 +3048,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>377.7382696589747</v>
+        <v>727.7651521517236</v>
       </c>
       <c r="K32" t="n">
-        <v>505.4012214189947</v>
+        <v>727.1079320762492</v>
       </c>
       <c r="L32" t="n">
         <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>256.9910820920259</v>
+        <v>304.6719533611628</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000412</v>
+        <v>153.5855355810893</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>329.9706110579529</v>
+        <v>329.9706110579538</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>295.6755817285639</v>
       </c>
       <c r="U32" t="n">
-        <v>358.2212965486107</v>
+        <v>366.6778879340249</v>
       </c>
       <c r="V32" t="n">
         <v>338.8510241668239</v>
@@ -3093,7 +3093,7 @@
         <v>301.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>228.7740240682207</v>
+        <v>220.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -3212,28 +3212,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>194.5984637871033</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>226.7541306595498</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3282,37 +3282,37 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I35" t="n">
-        <v>8.45659138541424</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>377.738269658982</v>
+        <v>757.6173000000483</v>
       </c>
       <c r="K35" t="n">
-        <v>712.5516968960405</v>
+        <v>317.2899665546989</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>256.9910820920331</v>
+        <v>256.991082092034</v>
       </c>
       <c r="N35" t="n">
-        <v>153.5855355810957</v>
+        <v>153.5855355810966</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="P35" t="n">
-        <v>757.6173000000472</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>757.6173000000472</v>
+        <v>757.6173000000481</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>203.8481678023229</v>
+        <v>212.3047591877378</v>
       </c>
       <c r="T35" t="n">
         <v>295.6755817285639</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>109.2047614405436</v>
+        <v>109.2047614405202</v>
       </c>
       <c r="P37" t="n">
         <v>396.4478973282775</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>190.9993129555745</v>
+        <v>199.4559043409888</v>
       </c>
       <c r="C38" t="n">
         <v>158.4745782429939</v>
@@ -3519,22 +3519,22 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I38" t="n">
-        <v>8.45659138541424</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>377.7382696589893</v>
+        <v>377.7382696589902</v>
       </c>
       <c r="K38" t="n">
-        <v>773</v>
+        <v>654.6988358539018</v>
       </c>
       <c r="L38" t="n">
-        <v>697.1689968957978</v>
+        <v>727.1079320759511</v>
       </c>
       <c r="M38" t="n">
-        <v>256.9910820920404</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="N38" t="n">
-        <v>153.5855355811029</v>
+        <v>153.5855355811038</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>757.6173000000545</v>
+        <v>329.9706110579683</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3686,25 +3686,25 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>298.1276103623819</v>
       </c>
       <c r="P40" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>108.4418998849671</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>268.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>197.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>191.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>190.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>195.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,10 +3783,10 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>37.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>200.9604583029384</v>
+        <v>281.8481678023229</v>
       </c>
       <c r="T41" t="n">
         <v>373.6755817285639</v>
@@ -3801,10 +3801,10 @@
         <v>425.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>379.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>298.3174326828064</v>
+        <v>19.90502879739792</v>
       </c>
     </row>
     <row r="42">
@@ -3862,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>196.8073545500588</v>
+        <v>334.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>253.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>192.3577652175138</v>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>10.12047485706833</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -3905,13 +3905,13 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>61.38285596774193</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>15.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>149.3734797028554</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3978,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>223.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -4020,10 +4020,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>63.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>307.8481678023229</v>
       </c>
       <c r="T44" t="n">
         <v>399.6755817285639</v>
@@ -4038,10 +4038,10 @@
         <v>451.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>405.2818334606677</v>
+        <v>316.5721081343499</v>
       </c>
       <c r="Y44" t="n">
-        <v>256.2381205906673</v>
+        <v>324.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4057,7 +4057,7 @@
         <v>174.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>160.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>155.6720972219126</v>
@@ -4066,10 +4066,10 @@
         <v>152.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>138.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>145.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>30.12638589134853</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>16.55705513387049</v>
+        <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>124.7726014430683</v>
       </c>
       <c r="T45" t="n">
         <v>218.3577652175138</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>41.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>702.4077201726793</v>
+        <v>954.8509932204727</v>
       </c>
       <c r="C2" t="n">
-        <v>652.4333987151097</v>
+        <v>500.836267722499</v>
       </c>
       <c r="D2" t="n">
-        <v>641.9898070586958</v>
+        <v>86.35227202568095</v>
       </c>
       <c r="E2" t="n">
-        <v>637.5824438194345</v>
+        <v>81.94490878641969</v>
       </c>
       <c r="F2" t="n">
-        <v>632.6434249224528</v>
+        <v>77.00588988943801</v>
       </c>
       <c r="G2" t="n">
-        <v>628.8480993800122</v>
+        <v>73.21056434699739</v>
       </c>
       <c r="H2" t="n">
-        <v>216.7171309926107</v>
+        <v>65.12</v>
       </c>
       <c r="I2" t="n">
         <v>65.12</v>
       </c>
       <c r="J2" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K2" t="n">
-        <v>772.8740581041409</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L2" t="n">
-        <v>1578.734058104141</v>
+        <v>1442.413279433291</v>
       </c>
       <c r="M2" t="n">
-        <v>1562.371835881919</v>
+        <v>1426.051057211069</v>
       </c>
       <c r="N2" t="n">
-        <v>2171.680789840457</v>
+        <v>2035.360011169607</v>
       </c>
       <c r="O2" t="n">
-        <v>2450.14</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P2" t="n">
-        <v>3256</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q2" t="n">
         <v>3256</v>
       </c>
       <c r="R2" t="n">
-        <v>3002.587273910814</v>
+        <v>3161.485463247056</v>
       </c>
       <c r="S2" t="n">
-        <v>2502.740639767053</v>
+        <v>3065.6792331437</v>
       </c>
       <c r="T2" t="n">
-        <v>1910.139042061433</v>
+        <v>2877.118039478483</v>
       </c>
       <c r="U2" t="n">
-        <v>1564.855274967447</v>
+        <v>2625.379356096048</v>
       </c>
       <c r="V2" t="n">
-        <v>1332.682523283786</v>
+        <v>2393.206604412388</v>
       </c>
       <c r="W2" t="n">
-        <v>1091.901234414142</v>
+        <v>2152.425315542744</v>
       </c>
       <c r="X2" t="n">
-        <v>897.6771602114478</v>
+        <v>1554.160837299645</v>
       </c>
       <c r="Y2" t="n">
-        <v>785.2353090166939</v>
+        <v>1441.718986104891</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2966.957099210679</v>
+        <v>543.0685532697942</v>
       </c>
       <c r="C3" t="n">
-        <v>2966.957099210679</v>
+        <v>543.0685532697942</v>
       </c>
       <c r="D3" t="n">
-        <v>2615.504890223101</v>
+        <v>543.0685532697942</v>
       </c>
       <c r="E3" t="n">
-        <v>2269.371458685815</v>
+        <v>543.0685532697942</v>
       </c>
       <c r="F3" t="n">
-        <v>2100.567579631464</v>
+        <v>200.0016418173932</v>
       </c>
       <c r="G3" t="n">
-        <v>2100.567579631464</v>
+        <v>200.0016418173932</v>
       </c>
       <c r="H3" t="n">
-        <v>2100.567579631464</v>
+        <v>65.12</v>
       </c>
       <c r="I3" t="n">
-        <v>2100.567579631464</v>
+        <v>65.12</v>
       </c>
       <c r="J3" t="n">
-        <v>2224.524099806763</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K3" t="n">
-        <v>2413.716915901147</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L3" t="n">
-        <v>2685.067377496347</v>
+        <v>649.6197978648825</v>
       </c>
       <c r="M3" t="n">
-        <v>2771.147919239206</v>
+        <v>735.7003396077417</v>
       </c>
       <c r="N3" t="n">
-        <v>2904.428203846775</v>
+        <v>868.9806242153101</v>
       </c>
       <c r="O3" t="n">
-        <v>3143.470655530493</v>
+        <v>1108.023075899029</v>
       </c>
       <c r="P3" t="n">
-        <v>3256</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>3256</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>3107.238588593556</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>3040.002224992939</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T3" t="n">
-        <v>3034.590340934844</v>
+        <v>999.1427613033796</v>
       </c>
       <c r="U3" t="n">
-        <v>3034.377856328595</v>
+        <v>998.9302766971304</v>
       </c>
       <c r="V3" t="n">
-        <v>3019.720616741201</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W3" t="n">
-        <v>2987.020472387838</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X3" t="n">
-        <v>2966.957099210679</v>
+        <v>931.509519579215</v>
       </c>
       <c r="Y3" t="n">
-        <v>2966.957099210679</v>
+        <v>931.509519579215</v>
       </c>
     </row>
     <row r="4">
@@ -4455,40 +4455,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>923.5983371018272</v>
+        <v>580.0072084245159</v>
       </c>
       <c r="C4" t="n">
-        <v>1028.860978117938</v>
+        <v>706.0092142429517</v>
       </c>
       <c r="D4" t="n">
-        <v>1142.180122242938</v>
+        <v>819.3283583679518</v>
       </c>
       <c r="E4" t="n">
-        <v>1142.180122242938</v>
+        <v>937.1572625793648</v>
       </c>
       <c r="F4" t="n">
-        <v>1266.541094834874</v>
+        <v>1061.5182351713</v>
       </c>
       <c r="G4" t="n">
-        <v>1266.541094834874</v>
+        <v>1214.924801058186</v>
       </c>
       <c r="H4" t="n">
-        <v>1436.057679994271</v>
+        <v>1214.924801058186</v>
       </c>
       <c r="I4" t="n">
-        <v>1436.057679994271</v>
+        <v>1436.057679994269</v>
       </c>
       <c r="J4" t="n">
-        <v>1436.057679994271</v>
+        <v>1436.057679994269</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.42211393114</v>
+        <v>1546.422113931137</v>
       </c>
       <c r="L4" t="n">
-        <v>1522.636630943484</v>
+        <v>1522.636630943481</v>
       </c>
       <c r="M4" t="n">
-        <v>1400.786518415656</v>
+        <v>1400.786518415653</v>
       </c>
       <c r="N4" t="n">
         <v>1257.377430115193</v>
@@ -4509,22 +4509,22 @@
         <v>102.3702550941731</v>
       </c>
       <c r="T4" t="n">
-        <v>290.445934252978</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="U4" t="n">
-        <v>290.445934252978</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="V4" t="n">
-        <v>489.2673271389239</v>
+        <v>257.085499140645</v>
       </c>
       <c r="W4" t="n">
-        <v>661.1582453986014</v>
+        <v>428.9764174003224</v>
       </c>
       <c r="X4" t="n">
-        <v>812.1890364227949</v>
+        <v>580.0072084245159</v>
       </c>
       <c r="Y4" t="n">
-        <v>923.5983371018272</v>
+        <v>580.0072084245159</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>391.9123998438256</v>
+        <v>1453.405934013821</v>
       </c>
       <c r="C5" t="n">
-        <v>341.938078386256</v>
+        <v>1403.431612556251</v>
       </c>
       <c r="D5" t="n">
-        <v>331.4944867298421</v>
+        <v>988.9476168594329</v>
       </c>
       <c r="E5" t="n">
-        <v>327.0871234905808</v>
+        <v>984.5402536201716</v>
       </c>
       <c r="F5" t="n">
-        <v>322.1481045935992</v>
+        <v>979.6012347231899</v>
       </c>
       <c r="G5" t="n">
-        <v>318.3527790511586</v>
+        <v>628.8480993800122</v>
       </c>
       <c r="H5" t="n">
         <v>216.7171309926107</v>
@@ -4558,52 +4558,52 @@
         <v>65.12</v>
       </c>
       <c r="J5" t="n">
-        <v>65.12</v>
+        <v>448.0120508495621</v>
       </c>
       <c r="K5" t="n">
-        <v>772.8740581041409</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L5" t="n">
-        <v>756.5118358819186</v>
+        <v>1961.626108953703</v>
       </c>
       <c r="M5" t="n">
-        <v>740.1496136596963</v>
+        <v>1945.263886731481</v>
       </c>
       <c r="N5" t="n">
-        <v>1349.458567618235</v>
+        <v>1928.901664509258</v>
       </c>
       <c r="O5" t="n">
-        <v>2155.318567618235</v>
+        <v>2018.997788947385</v>
       </c>
       <c r="P5" t="n">
-        <v>2961.178567618235</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q5" t="n">
         <v>3256</v>
       </c>
       <c r="R5" t="n">
-        <v>3002.587273910814</v>
+        <v>3256</v>
       </c>
       <c r="S5" t="n">
-        <v>2502.740639767053</v>
+        <v>3160.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>1910.139042061433</v>
+        <v>2971.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>1254.359954638594</v>
+        <v>2315.853488808588</v>
       </c>
       <c r="V5" t="n">
-        <v>1022.187202954933</v>
+        <v>2083.680737124928</v>
       </c>
       <c r="W5" t="n">
-        <v>781.4059140852889</v>
+        <v>1842.899448255284</v>
       </c>
       <c r="X5" t="n">
-        <v>587.1818398825942</v>
+        <v>1648.675374052589</v>
       </c>
       <c r="Y5" t="n">
-        <v>474.7399886878403</v>
+        <v>1536.233522857835</v>
       </c>
     </row>
     <row r="6">
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="C6" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="D6" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="E6" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="F6" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="G6" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="H6" t="n">
         <v>65.12</v>
@@ -4661,28 +4661,28 @@
         <v>1220.552420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>667.7506049216878</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>600.5142413210704</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T6" t="n">
-        <v>595.1023572629756</v>
+        <v>872.3169661548932</v>
       </c>
       <c r="U6" t="n">
-        <v>190.8494686163223</v>
+        <v>872.1044815486439</v>
       </c>
       <c r="V6" t="n">
-        <v>117.8835175305213</v>
+        <v>453.4068379208456</v>
       </c>
       <c r="W6" t="n">
-        <v>85.18337317715914</v>
+        <v>420.7066935674835</v>
       </c>
       <c r="X6" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="Y6" t="n">
-        <v>65.12</v>
+        <v>400.6433203903244</v>
       </c>
     </row>
     <row r="7">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>659.1521412974381</v>
+        <v>688.027917915458</v>
       </c>
       <c r="C7" t="n">
-        <v>785.1541471158739</v>
+        <v>688.027917915458</v>
       </c>
       <c r="D7" t="n">
-        <v>898.473291240874</v>
+        <v>688.027917915458</v>
       </c>
       <c r="E7" t="n">
-        <v>1016.302195452287</v>
+        <v>805.8568221268711</v>
       </c>
       <c r="F7" t="n">
-        <v>1140.663168044223</v>
+        <v>930.2177947188065</v>
       </c>
       <c r="G7" t="n">
-        <v>1294.069733931108</v>
+        <v>1083.624360605692</v>
       </c>
       <c r="H7" t="n">
-        <v>1325.28923499506</v>
+        <v>1253.14094576509</v>
       </c>
       <c r="I7" t="n">
-        <v>1546.422113931143</v>
+        <v>1474.273824701173</v>
       </c>
       <c r="J7" t="n">
-        <v>1546.422113931143</v>
+        <v>1474.273824701173</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931143</v>
+        <v>1546.422113931142</v>
       </c>
       <c r="L7" t="n">
-        <v>1546.422113931143</v>
+        <v>1546.422113931142</v>
       </c>
       <c r="M7" t="n">
-        <v>1424.572001403315</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N7" t="n">
-        <v>1251.657783957168</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O7" t="n">
-        <v>1008.783476806648</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P7" t="n">
-        <v>718.4320653639438</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q7" t="n">
-        <v>389.3014932168751</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R7" t="n">
         <v>65.12</v>
@@ -4746,22 +4746,22 @@
         <v>102.3702550941731</v>
       </c>
       <c r="T7" t="n">
-        <v>102.3702550941731</v>
+        <v>290.445934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>348.9214477324598</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="V7" t="n">
-        <v>547.7428406184058</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="W7" t="n">
-        <v>547.7428406184058</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="X7" t="n">
-        <v>547.7428406184058</v>
+        <v>688.027917915458</v>
       </c>
       <c r="Y7" t="n">
-        <v>659.1521412974381</v>
+        <v>688.027917915458</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>298.3673161322752</v>
+        <v>1453.405934013821</v>
       </c>
       <c r="C8" t="n">
-        <v>248.3929946747056</v>
+        <v>1403.431612556251</v>
       </c>
       <c r="D8" t="n">
-        <v>237.9494030182917</v>
+        <v>1392.988020899837</v>
       </c>
       <c r="E8" t="n">
-        <v>233.5420397790304</v>
+        <v>1041.622847859839</v>
       </c>
       <c r="F8" t="n">
-        <v>228.6030208820488</v>
+        <v>632.6434249224528</v>
       </c>
       <c r="G8" t="n">
-        <v>224.8076953396081</v>
+        <v>628.8480993800122</v>
       </c>
       <c r="H8" t="n">
         <v>216.7171309926107</v>
@@ -4798,22 +4798,22 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>431.6498286273397</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L8" t="n">
-        <v>921.1921502332721</v>
+        <v>1677.004444444444</v>
       </c>
       <c r="M8" t="n">
-        <v>1426.051057211065</v>
+        <v>1660.642222222222</v>
       </c>
       <c r="N8" t="n">
-        <v>2035.360011169603</v>
+        <v>1644.28</v>
       </c>
       <c r="O8" t="n">
-        <v>2841.220011169603</v>
+        <v>2450.14</v>
       </c>
       <c r="P8" t="n">
-        <v>2824.857788947385</v>
+        <v>3256</v>
       </c>
       <c r="Q8" t="n">
         <v>3256</v>
@@ -4825,22 +4825,22 @@
         <v>3160.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>2567.592172191024</v>
+        <v>2971.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>1911.813084768185</v>
+        <v>2315.853488808588</v>
       </c>
       <c r="V8" t="n">
-        <v>1275.59992904412</v>
+        <v>2083.680737124928</v>
       </c>
       <c r="W8" t="n">
-        <v>1034.818640174476</v>
+        <v>1842.899448255284</v>
       </c>
       <c r="X8" t="n">
-        <v>840.5945659717813</v>
+        <v>1648.675374052589</v>
       </c>
       <c r="Y8" t="n">
-        <v>728.1527147770274</v>
+        <v>1536.233522857835</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12</v>
+        <v>566.7621332706096</v>
       </c>
       <c r="D9" t="n">
-        <v>65.12</v>
+        <v>411.2534315372855</v>
       </c>
       <c r="E9" t="n">
         <v>65.12</v>
@@ -4895,31 +4895,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1045.724879873102</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>492.9230644262537</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>425.6867008256363</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T9" t="n">
-        <v>132.7532417241646</v>
+        <v>999.1427613033796</v>
       </c>
       <c r="U9" t="n">
-        <v>132.5407571179154</v>
+        <v>998.9302766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>117.8835175305213</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>85.18337317715914</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X9" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
     </row>
     <row r="10">
@@ -4929,37 +4929,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>584.8399039060887</v>
+        <v>410.4906232651222</v>
       </c>
       <c r="C10" t="n">
-        <v>710.8419097245245</v>
+        <v>536.492629083558</v>
       </c>
       <c r="D10" t="n">
-        <v>824.1610538495246</v>
+        <v>649.8117732085581</v>
       </c>
       <c r="E10" t="n">
-        <v>941.9899580609376</v>
+        <v>767.6406774199711</v>
       </c>
       <c r="F10" t="n">
-        <v>1066.350930652873</v>
+        <v>892.0016500119066</v>
       </c>
       <c r="G10" t="n">
-        <v>1219.757496539758</v>
+        <v>1045.408215898792</v>
       </c>
       <c r="H10" t="n">
-        <v>1219.757496539758</v>
+        <v>1214.92480105819</v>
       </c>
       <c r="I10" t="n">
-        <v>1436.057679994274</v>
+        <v>1436.057679994273</v>
       </c>
       <c r="J10" t="n">
-        <v>1436.057679994274</v>
+        <v>1436.057679994273</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.422113931143</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="L10" t="n">
-        <v>1546.422113931143</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="M10" t="n">
         <v>1430.29164756134</v>
@@ -4980,25 +4980,25 @@
         <v>65.12</v>
       </c>
       <c r="S10" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T10" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="U10" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="V10" t="n">
-        <v>301.1916479801191</v>
+        <v>65.12</v>
       </c>
       <c r="W10" t="n">
-        <v>473.0825662397965</v>
+        <v>65.12</v>
       </c>
       <c r="X10" t="n">
-        <v>473.0825662397965</v>
+        <v>216.1507910241935</v>
       </c>
       <c r="Y10" t="n">
-        <v>473.0825662397965</v>
+        <v>327.5600917032258</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>417.1649250963513</v>
+        <v>1207.376245745725</v>
       </c>
       <c r="C11" t="n">
-        <v>249.9782411146742</v>
+        <v>980.6342475204788</v>
       </c>
       <c r="D11" t="n">
-        <v>249.9782411146742</v>
+        <v>793.4229790963881</v>
       </c>
       <c r="E11" t="n">
-        <v>249.9782411146742</v>
+        <v>612.24793908945</v>
       </c>
       <c r="F11" t="n">
-        <v>249.9782411146742</v>
+        <v>430.5412434247916</v>
       </c>
       <c r="G11" t="n">
         <v>249.9782411146742</v>
@@ -5032,22 +5032,22 @@
         <v>65.12</v>
       </c>
       <c r="J11" t="n">
-        <v>65.12</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>774.8263663478684</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1580.686366347868</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>2091.535195076804</v>
+        <v>1398.320585172569</v>
       </c>
       <c r="N11" t="n">
-        <v>2704.755514851567</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>2704.755514851567</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="P11" t="n">
         <v>2817.400904947332</v>
@@ -5059,25 +5059,25 @@
         <v>3229.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>2957.286094312508</v>
+        <v>3087.29613602908</v>
       </c>
       <c r="T11" t="n">
-        <v>2591.957223879615</v>
+        <v>2721.967265596187</v>
       </c>
       <c r="U11" t="n">
-        <v>2163.450863729503</v>
+        <v>2293.460905446075</v>
       </c>
       <c r="V11" t="n">
-        <v>1754.510435278166</v>
+        <v>1884.520476994737</v>
       </c>
       <c r="W11" t="n">
-        <v>1336.961469640845</v>
+        <v>1466.971511357417</v>
       </c>
       <c r="X11" t="n">
-        <v>965.9697186704734</v>
+        <v>1466.971511357417</v>
       </c>
       <c r="Y11" t="n">
-        <v>676.7601907080427</v>
+        <v>1466.971511357417</v>
       </c>
     </row>
     <row r="12">
@@ -5117,13 +5117,13 @@
         <v>831.5642142372474</v>
       </c>
       <c r="L12" t="n">
-        <v>1325.664675832448</v>
+        <v>1121.840378378698</v>
       </c>
       <c r="M12" t="n">
-        <v>1634.495217575307</v>
+        <v>1430.670920121557</v>
       </c>
       <c r="N12" t="n">
-        <v>1990.525502182875</v>
+        <v>1786.701204729125</v>
       </c>
       <c r="O12" t="n">
         <v>2248.493656412844</v>
@@ -5208,10 +5208,10 @@
         <v>409.3389893823512</v>
       </c>
       <c r="P13" t="n">
-        <v>65.12</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.12</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="R13" t="n">
         <v>65.12</v>
@@ -5257,7 +5257,7 @@
         <v>291.9779198897361</v>
       </c>
       <c r="F14" t="n">
-        <v>223.7156148520479</v>
+        <v>291.9779198897361</v>
       </c>
       <c r="G14" t="n">
         <v>223.7156148520479</v>
@@ -5278,10 +5278,10 @@
         <v>456.4291130376557</v>
       </c>
       <c r="M14" t="n">
-        <v>967.2779417665907</v>
+        <v>592.460585172569</v>
       </c>
       <c r="N14" t="n">
-        <v>1580.498261541354</v>
+        <v>1205.680904947332</v>
       </c>
       <c r="O14" t="n">
         <v>2011.540904947332</v>
@@ -5348,22 +5348,22 @@
         <v>98.65487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>222.6113981428639</v>
+        <v>471.1013981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>411.8042142372473</v>
+        <v>908.7842142372473</v>
       </c>
       <c r="L15" t="n">
-        <v>683.1546758324473</v>
+        <v>1428.624675832447</v>
       </c>
       <c r="M15" t="n">
-        <v>933.7715261821634</v>
+        <v>1514.705217575307</v>
       </c>
       <c r="N15" t="n">
-        <v>1315.541810789732</v>
+        <v>1647.985502182875</v>
       </c>
       <c r="O15" t="n">
-        <v>1803.074262473451</v>
+        <v>1887.027953866594</v>
       </c>
       <c r="P15" t="n">
         <v>2164.093606942957</v>
@@ -5448,10 +5448,10 @@
         <v>599.0397446017254</v>
       </c>
       <c r="Q16" t="n">
-        <v>545.5261898799506</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="R16" t="n">
-        <v>65.12</v>
+        <v>118.6335547217748</v>
       </c>
       <c r="S16" t="n">
         <v>65.12</v>
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>879.6685602764463</v>
+        <v>880.1035184729978</v>
       </c>
       <c r="C17" t="n">
-        <v>707.4720165966545</v>
+        <v>707.906974793206</v>
       </c>
       <c r="D17" t="n">
-        <v>574.8062027180183</v>
+        <v>575.2411609145698</v>
       </c>
       <c r="E17" t="n">
-        <v>448.1766172565348</v>
+        <v>448.6115754530863</v>
       </c>
       <c r="F17" t="n">
         <v>321.4503343338824</v>
@@ -5512,19 +5512,19 @@
         <v>1166.135479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>1166.135479385524</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="M17" t="n">
-        <v>1166.135479385524</v>
+        <v>2482.844308114459</v>
       </c>
       <c r="N17" t="n">
-        <v>1205.680904947332</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="O17" t="n">
-        <v>2011.540904947332</v>
+        <v>3256</v>
       </c>
       <c r="P17" t="n">
-        <v>2817.400904947332</v>
+        <v>3256</v>
       </c>
       <c r="Q17" t="n">
         <v>3256</v>
@@ -5533,25 +5533,25 @@
         <v>3256</v>
       </c>
       <c r="S17" t="n">
-        <v>3037.971547674421</v>
+        <v>3038.406505870973</v>
       </c>
       <c r="T17" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.623089983534</v>
       </c>
       <c r="U17" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.662184378877</v>
       </c>
       <c r="V17" t="n">
-        <v>1998.832252276443</v>
+        <v>1999.267210472994</v>
       </c>
       <c r="W17" t="n">
-        <v>1635.828741184576</v>
+        <v>1636.263699381128</v>
       </c>
       <c r="X17" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.817402956211</v>
       </c>
       <c r="Y17" t="n">
-        <v>1084.718371342683</v>
+        <v>1085.153329539235</v>
       </c>
     </row>
     <row r="18">
@@ -5582,28 +5582,28 @@
         <v>65.12</v>
       </c>
       <c r="I18" t="n">
-        <v>126.374877967565</v>
+        <v>109.1402898924222</v>
       </c>
       <c r="J18" t="n">
-        <v>404.4452825072959</v>
+        <v>233.0968100677211</v>
       </c>
       <c r="K18" t="n">
-        <v>593.6380986016793</v>
+        <v>422.2896261621045</v>
       </c>
       <c r="L18" t="n">
-        <v>864.9885601968793</v>
+        <v>693.6400877573046</v>
       </c>
       <c r="M18" t="n">
-        <v>951.0691019397386</v>
+        <v>779.7206295001639</v>
       </c>
       <c r="N18" t="n">
-        <v>1084.349386547307</v>
+        <v>913.0009141077322</v>
       </c>
       <c r="O18" t="n">
-        <v>1323.391838231026</v>
+        <v>1428.253365791451</v>
       </c>
       <c r="P18" t="n">
-        <v>1712.131182700533</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="Q18" t="n">
         <v>1816.992710260958</v>
@@ -5640,55 +5640,55 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>414.3442160506673</v>
+        <v>405.793354586564</v>
       </c>
       <c r="C19" t="n">
-        <v>420.5562218691031</v>
+        <v>412.0053604049997</v>
       </c>
       <c r="D19" t="n">
-        <v>413.953981408946</v>
+        <v>405.4031199448427</v>
       </c>
       <c r="E19" t="n">
-        <v>413.953981408946</v>
+        <v>403.4022059681189</v>
       </c>
       <c r="F19" t="n">
-        <v>418.5249540008816</v>
+        <v>407.9731785600544</v>
       </c>
       <c r="G19" t="n">
-        <v>452.1415198877668</v>
+        <v>441.5897444469397</v>
       </c>
       <c r="H19" t="n">
-        <v>501.8681050471644</v>
+        <v>491.3163296063373</v>
       </c>
       <c r="I19" t="n">
-        <v>603.2109839832474</v>
+        <v>592.6592085424202</v>
       </c>
       <c r="J19" t="n">
-        <v>844.5047246356987</v>
+        <v>833.9529491948715</v>
       </c>
       <c r="K19" t="n">
-        <v>844.5047246356987</v>
+        <v>824.3360059613937</v>
       </c>
       <c r="L19" t="n">
-        <v>844.5047246356987</v>
+        <v>678.3283007515157</v>
       </c>
       <c r="M19" t="n">
-        <v>844.5047246356987</v>
+        <v>434.2559660014653</v>
       </c>
       <c r="N19" t="n">
-        <v>844.5047246356987</v>
+        <v>139.1195263330967</v>
       </c>
       <c r="O19" t="n">
-        <v>844.5047246356987</v>
+        <v>139.1195263330967</v>
       </c>
       <c r="P19" t="n">
-        <v>844.5047246356987</v>
+        <v>139.1195263330967</v>
       </c>
       <c r="Q19" t="n">
-        <v>601.4589976606127</v>
+        <v>139.1195263330967</v>
       </c>
       <c r="R19" t="n">
-        <v>149.3356360634903</v>
+        <v>139.1195263330967</v>
       </c>
       <c r="S19" t="n">
         <v>65.12</v>
@@ -5709,7 +5709,7 @@
         <v>422.5399739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>422.5399739669084</v>
+        <v>413.989112502805</v>
       </c>
     </row>
     <row r="20">
@@ -5743,19 +5743,19 @@
         <v>65.12</v>
       </c>
       <c r="J20" t="n">
-        <v>456.4291130376557</v>
+        <v>65.12</v>
       </c>
       <c r="K20" t="n">
-        <v>456.4291130376557</v>
+        <v>774.8263663478684</v>
       </c>
       <c r="L20" t="n">
-        <v>694.8320762183972</v>
+        <v>1580.686366347868</v>
       </c>
       <c r="M20" t="n">
-        <v>1205.680904947332</v>
+        <v>1580.686366347869</v>
       </c>
       <c r="N20" t="n">
-        <v>1205.680904947332</v>
+        <v>1580.686366347869</v>
       </c>
       <c r="O20" t="n">
         <v>2011.540904947332</v>
@@ -5822,25 +5822,25 @@
         <v>126.374877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>526.5413981428638</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>869.8480986016793</v>
+        <v>439.5242142372473</v>
       </c>
       <c r="L21" t="n">
-        <v>1141.198560196879</v>
+        <v>710.8746758324473</v>
       </c>
       <c r="M21" t="n">
-        <v>1227.279101939739</v>
+        <v>796.9552175753066</v>
       </c>
       <c r="N21" t="n">
-        <v>1360.559386547307</v>
+        <v>930.2355021828749</v>
       </c>
       <c r="O21" t="n">
-        <v>1599.601838231026</v>
+        <v>1445.487953866594</v>
       </c>
       <c r="P21" t="n">
-        <v>1712.131182700533</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="Q21" t="n">
         <v>1816.992710260958</v>
@@ -5877,55 +5877,55 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>422.5399739669084</v>
+        <v>405.793354586564</v>
       </c>
       <c r="C22" t="n">
-        <v>428.7519797853442</v>
+        <v>412.0053604049997</v>
       </c>
       <c r="D22" t="n">
-        <v>428.7519797853442</v>
+        <v>405.4031199448427</v>
       </c>
       <c r="E22" t="n">
-        <v>428.7519797853442</v>
+        <v>404.0013724650347</v>
       </c>
       <c r="F22" t="n">
-        <v>433.3229523772797</v>
+        <v>408.5723450569702</v>
       </c>
       <c r="G22" t="n">
-        <v>466.939518264165</v>
+        <v>442.1889109438555</v>
       </c>
       <c r="H22" t="n">
-        <v>516.6661034235625</v>
+        <v>491.9154961032531</v>
       </c>
       <c r="I22" t="n">
-        <v>618.0089823596454</v>
+        <v>593.258375039336</v>
       </c>
       <c r="J22" t="n">
-        <v>859.3027230120967</v>
+        <v>834.5521156917873</v>
       </c>
       <c r="K22" t="n">
-        <v>859.3027230120967</v>
+        <v>834.5521156917873</v>
       </c>
       <c r="L22" t="n">
-        <v>859.3027230120967</v>
+        <v>688.5444104819094</v>
       </c>
       <c r="M22" t="n">
-        <v>859.3027230120967</v>
+        <v>444.4720757318589</v>
       </c>
       <c r="N22" t="n">
-        <v>859.3027230120967</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="O22" t="n">
-        <v>859.3027230120967</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="P22" t="n">
-        <v>516.472794369291</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="Q22" t="n">
-        <v>65.12</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="R22" t="n">
-        <v>65.12</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="S22" t="n">
         <v>65.12</v>
@@ -5946,7 +5946,7 @@
         <v>422.5399739669084</v>
       </c>
       <c r="Y22" t="n">
-        <v>422.5399739669084</v>
+        <v>413.989112502805</v>
       </c>
     </row>
     <row r="23">
@@ -5983,16 +5983,16 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>456.4291130376557</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L23" t="n">
-        <v>694.8320762183972</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="M23" t="n">
-        <v>1205.680904947332</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="N23" t="n">
-        <v>1205.680904947332</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="O23" t="n">
         <v>2011.540904947332</v>
@@ -6059,22 +6059,22 @@
         <v>126.374877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>526.5413981428638</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>715.7342142372472</v>
+        <v>439.5242142372473</v>
       </c>
       <c r="L24" t="n">
-        <v>987.0846758324474</v>
+        <v>710.8746758324473</v>
       </c>
       <c r="M24" t="n">
         <v>1073.165217575307</v>
       </c>
       <c r="N24" t="n">
-        <v>1206.445502182875</v>
+        <v>1360.559386547307</v>
       </c>
       <c r="O24" t="n">
-        <v>1445.487953866594</v>
+        <v>1599.601838231026</v>
       </c>
       <c r="P24" t="n">
         <v>1712.131182700533</v>
@@ -6144,22 +6144,22 @@
         <v>859.3027230120967</v>
       </c>
       <c r="L25" t="n">
-        <v>713.2950178022188</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="M25" t="n">
-        <v>469.2226830521684</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="N25" t="n">
-        <v>174.0862433837998</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="O25" t="n">
-        <v>65.12</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P25" t="n">
-        <v>65.12</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q25" t="n">
-        <v>65.12</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="R25" t="n">
         <v>65.12</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1204.096245745725</v>
+        <v>253.1649250963515</v>
       </c>
       <c r="C26" t="n">
-        <v>977.3542475204788</v>
+        <v>61.84</v>
       </c>
       <c r="D26" t="n">
-        <v>790.1429790963881</v>
+        <v>61.84</v>
       </c>
       <c r="E26" t="n">
-        <v>608.9679390894501</v>
+        <v>61.84</v>
       </c>
       <c r="F26" t="n">
-        <v>427.2612434247916</v>
+        <v>61.84</v>
       </c>
       <c r="G26" t="n">
-        <v>246.6982411146742</v>
+        <v>61.84</v>
       </c>
       <c r="H26" t="n">
         <v>61.84</v>
@@ -6220,22 +6220,22 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K26" t="n">
-        <v>453.1491130376558</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>1218.419113037656</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>1729.267941766591</v>
+        <v>1673.704308114459</v>
       </c>
       <c r="N26" t="n">
-        <v>1729.267941766591</v>
+        <v>1888.130904947305</v>
       </c>
       <c r="O26" t="n">
-        <v>2326.729999999974</v>
+        <v>1888.130904947305</v>
       </c>
       <c r="P26" t="n">
-        <v>3092</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="Q26" t="n">
         <v>3092</v>
@@ -6244,25 +6244,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>3065.860001183541</v>
+        <v>2793.286094312508</v>
       </c>
       <c r="T26" t="n">
-        <v>3065.860001183541</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="U26" t="n">
-        <v>2637.353641033429</v>
+        <v>1999.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>2228.413212582092</v>
+        <v>1590.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1810.864246944771</v>
+        <v>1172.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>1439.872495974399</v>
+        <v>801.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>1439.872495974399</v>
+        <v>512.760190708043</v>
       </c>
     </row>
     <row r="27">
@@ -6293,22 +6293,22 @@
         <v>61.84</v>
       </c>
       <c r="I27" t="n">
-        <v>61.84</v>
+        <v>69.63487796756496</v>
       </c>
       <c r="J27" t="n">
-        <v>408.546520175299</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>820.4893362696823</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1314.589797864882</v>
+        <v>1322.384675832448</v>
       </c>
       <c r="M27" t="n">
-        <v>1623.420339607742</v>
+        <v>1631.215217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1979.45062421531</v>
+        <v>1987.245502182875</v>
       </c>
       <c r="O27" t="n">
         <v>2245.213656412845</v>
@@ -6351,55 +6351,55 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="C28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="D28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="E28" t="n">
-        <v>128.550387991434</v>
+        <v>117.6052195561019</v>
       </c>
       <c r="F28" t="n">
-        <v>128.550387991434</v>
+        <v>117.6052195561019</v>
       </c>
       <c r="G28" t="n">
-        <v>128.550387991434</v>
+        <v>97.3588833525362</v>
       </c>
       <c r="H28" t="n">
-        <v>124.7411697069708</v>
+        <v>93.54966506807294</v>
       </c>
       <c r="I28" t="n">
-        <v>172.6240486430537</v>
+        <v>141.4325440041559</v>
       </c>
       <c r="J28" t="n">
-        <v>360.457789295505</v>
+        <v>329.2662846566072</v>
       </c>
       <c r="K28" t="n">
-        <v>360.457789295505</v>
+        <v>329.2662846566072</v>
       </c>
       <c r="L28" t="n">
-        <v>360.457789295505</v>
+        <v>329.2662846566072</v>
       </c>
       <c r="M28" t="n">
-        <v>61.84</v>
+        <v>329.2662846566072</v>
       </c>
       <c r="N28" t="n">
-        <v>61.84</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="O28" t="n">
-        <v>61.84</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="P28" t="n">
-        <v>61.84</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.84</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="R28" t="n">
-        <v>61.84</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="S28" t="n">
         <v>61.84</v>
@@ -6417,10 +6417,10 @@
         <v>174.1515880782802</v>
       </c>
       <c r="X28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="Y28" t="n">
-        <v>151.4812391589797</v>
+        <v>174.1515880782802</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>253.1649250963515</v>
+        <v>1099.220250883784</v>
       </c>
       <c r="C29" t="n">
-        <v>61.84</v>
+        <v>872.4782526585377</v>
       </c>
       <c r="D29" t="n">
-        <v>61.84</v>
+        <v>685.266984234447</v>
       </c>
       <c r="E29" t="n">
-        <v>61.84</v>
+        <v>504.091944227509</v>
       </c>
       <c r="F29" t="n">
-        <v>61.84</v>
+        <v>322.3852485628505</v>
       </c>
       <c r="G29" t="n">
-        <v>61.84</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="H29" t="n">
         <v>61.84</v>
@@ -6466,10 +6466,10 @@
         <v>963.9979417665908</v>
       </c>
       <c r="N29" t="n">
-        <v>1577.218261541354</v>
+        <v>1561.459999999931</v>
       </c>
       <c r="O29" t="n">
-        <v>2342.488261541388</v>
+        <v>2326.729999999965</v>
       </c>
       <c r="P29" t="n">
         <v>3092</v>
@@ -6487,19 +6487,19 @@
         <v>2427.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>1999.450863729503</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="V29" t="n">
-        <v>1590.510435278166</v>
+        <v>2019.016795428278</v>
       </c>
       <c r="W29" t="n">
-        <v>1172.961469640845</v>
+        <v>2019.016795428278</v>
       </c>
       <c r="X29" t="n">
-        <v>801.9697186704736</v>
+        <v>1648.025044457906</v>
       </c>
       <c r="Y29" t="n">
-        <v>512.760190708043</v>
+        <v>1358.815516495476</v>
       </c>
     </row>
     <row r="30">
@@ -6588,52 +6588,52 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>174.1515880782802</v>
+        <v>124.7411697069708</v>
       </c>
       <c r="C31" t="n">
-        <v>174.1515880782802</v>
+        <v>124.7411697069708</v>
       </c>
       <c r="D31" t="n">
-        <v>174.1515880782802</v>
+        <v>124.7411697069708</v>
       </c>
       <c r="E31" t="n">
-        <v>174.1515880782802</v>
+        <v>124.7411697069708</v>
       </c>
       <c r="F31" t="n">
-        <v>174.1515880782802</v>
+        <v>124.7411697069708</v>
       </c>
       <c r="G31" t="n">
-        <v>174.1515880782802</v>
+        <v>124.7411697069708</v>
       </c>
       <c r="H31" t="n">
-        <v>170.342369793817</v>
+        <v>124.7411697069708</v>
       </c>
       <c r="I31" t="n">
-        <v>218.2252487298999</v>
+        <v>172.6240486430537</v>
       </c>
       <c r="J31" t="n">
-        <v>406.0589893823512</v>
+        <v>360.457789295505</v>
       </c>
       <c r="K31" t="n">
-        <v>406.0589893823512</v>
+        <v>360.457789295505</v>
       </c>
       <c r="L31" t="n">
-        <v>406.0589893823512</v>
+        <v>360.457789295505</v>
       </c>
       <c r="M31" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="N31" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="O31" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="P31" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="Q31" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="R31" t="n">
         <v>61.84</v>
@@ -6657,7 +6657,7 @@
         <v>174.1515880782802</v>
       </c>
       <c r="Y31" t="n">
-        <v>174.1515880782802</v>
+        <v>124.7411697069708</v>
       </c>
     </row>
     <row r="32">
@@ -6691,19 +6691,19 @@
         <v>61.84</v>
       </c>
       <c r="J32" t="n">
-        <v>445.5561922637026</v>
+        <v>91.9936846952703</v>
       </c>
       <c r="K32" t="n">
-        <v>654.8867607573928</v>
+        <v>77.37808080808094</v>
       </c>
       <c r="L32" t="n">
-        <v>639.3486799493119</v>
+        <v>61.84</v>
       </c>
       <c r="M32" t="n">
-        <v>1145.031728341246</v>
+        <v>519.3605521604833</v>
       </c>
       <c r="N32" t="n">
-        <v>1129.493647533164</v>
+        <v>1129.493647533162</v>
       </c>
       <c r="O32" t="n">
         <v>1894.763647533204</v>
@@ -6724,16 +6724,16 @@
         <v>2587.430556029407</v>
       </c>
       <c r="U32" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V32" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W32" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X32" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y32" t="n">
         <v>997.0248446907499</v>
@@ -6770,25 +6770,25 @@
         <v>134.974877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>258.9313981428639</v>
+        <v>547.0213981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>448.1242142372473</v>
+        <v>736.2142142372472</v>
       </c>
       <c r="L33" t="n">
-        <v>719.4746758324475</v>
+        <v>1060.961905939123</v>
       </c>
       <c r="M33" t="n">
-        <v>805.5552175753068</v>
+        <v>1147.042447681983</v>
       </c>
       <c r="N33" t="n">
-        <v>938.8355021828751</v>
+        <v>1280.322732289551</v>
       </c>
       <c r="O33" t="n">
-        <v>1177.877953866594</v>
+        <v>1519.36518397327</v>
       </c>
       <c r="P33" t="n">
-        <v>1578.497298336101</v>
+        <v>1631.894528442776</v>
       </c>
       <c r="Q33" t="n">
         <v>1631.894528442776</v>
@@ -6825,55 +6825,55 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>486.0066123122328</v>
+        <v>486.0066123122566</v>
       </c>
       <c r="C34" t="n">
-        <v>504.0986181306686</v>
+        <v>504.0986181306923</v>
       </c>
       <c r="D34" t="n">
-        <v>509.5077622556687</v>
+        <v>509.5077622556924</v>
       </c>
       <c r="E34" t="n">
-        <v>519.4266664670818</v>
+        <v>519.4266664671054</v>
       </c>
       <c r="F34" t="n">
-        <v>535.8776390590173</v>
+        <v>535.8776390590409</v>
       </c>
       <c r="G34" t="n">
-        <v>581.3742049459025</v>
+        <v>581.3742049459262</v>
       </c>
       <c r="H34" t="n">
-        <v>642.9807901053001</v>
+        <v>642.9807901053238</v>
       </c>
       <c r="I34" t="n">
-        <v>756.203669041383</v>
+        <v>756.2036690414067</v>
       </c>
       <c r="J34" t="n">
-        <v>1009.377409693834</v>
+        <v>1009.377409693858</v>
       </c>
       <c r="K34" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="L34" t="n">
-        <v>1011.831843630703</v>
+        <v>877.9453505420606</v>
       </c>
       <c r="M34" t="n">
-        <v>1011.831843630703</v>
+        <v>645.9942279132224</v>
       </c>
       <c r="N34" t="n">
-        <v>815.2677387952449</v>
+        <v>362.9790003660659</v>
       </c>
       <c r="O34" t="n">
-        <v>462.2924215437147</v>
+        <v>362.9790003660659</v>
       </c>
       <c r="P34" t="n">
-        <v>61.84</v>
+        <v>362.9790003660659</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.84</v>
+        <v>362.9790003660659</v>
       </c>
       <c r="R34" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="S34" t="n">
         <v>61.84</v>
@@ -6894,7 +6894,7 @@
         <v>478.6599739669085</v>
       </c>
       <c r="Y34" t="n">
-        <v>482.1592746459407</v>
+        <v>482.1592746459644</v>
       </c>
     </row>
     <row r="35">
@@ -6904,46 +6904,46 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C35" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D35" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E35" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F35" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G35" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H35" t="n">
-        <v>70.38201150041843</v>
+        <v>61.84</v>
       </c>
       <c r="I35" t="n">
         <v>61.84</v>
       </c>
       <c r="J35" t="n">
-        <v>445.5561922637025</v>
+        <v>61.84</v>
       </c>
       <c r="K35" t="n">
-        <v>445.6438562353401</v>
+        <v>506.6150842881829</v>
       </c>
       <c r="L35" t="n">
-        <v>1210.91385623534</v>
+        <v>1226.451937043421</v>
       </c>
       <c r="M35" t="n">
-        <v>1716.596904627274</v>
+        <v>1732.134985435355</v>
       </c>
       <c r="N35" t="n">
-        <v>2326.729999999952</v>
+        <v>2342.268080808033</v>
       </c>
       <c r="O35" t="n">
-        <v>3092</v>
+        <v>2326.729999999951</v>
       </c>
       <c r="P35" t="n">
         <v>3092</v>
@@ -6955,25 +6955,25 @@
         <v>3092</v>
       </c>
       <c r="S35" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T35" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U35" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V35" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W35" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X35" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y35" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="36">
@@ -7004,22 +7004,22 @@
         <v>61.84</v>
       </c>
       <c r="I36" t="n">
-        <v>134.974877967565</v>
+        <v>61.84</v>
       </c>
       <c r="J36" t="n">
-        <v>258.9313981428639</v>
+        <v>185.796520175299</v>
       </c>
       <c r="K36" t="n">
-        <v>672.869916783498</v>
+        <v>374.9893362696823</v>
       </c>
       <c r="L36" t="n">
-        <v>944.220378378698</v>
+        <v>646.3397978648825</v>
       </c>
       <c r="M36" t="n">
-        <v>1030.300920121557</v>
+        <v>732.4203396077418</v>
       </c>
       <c r="N36" t="n">
-        <v>1163.581204729126</v>
+        <v>875.4912047291255</v>
       </c>
       <c r="O36" t="n">
         <v>1402.623656412844</v>
@@ -7062,43 +7062,43 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>486.0066123122566</v>
+        <v>486.0066123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>504.0986181306923</v>
+        <v>504.0986181306686</v>
       </c>
       <c r="D37" t="n">
-        <v>509.5077622556924</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E37" t="n">
-        <v>519.4266664671054</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F37" t="n">
-        <v>535.8776390590409</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G37" t="n">
-        <v>581.3742049459262</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H37" t="n">
-        <v>642.9807901053238</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I37" t="n">
-        <v>756.2036690414067</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J37" t="n">
-        <v>1009.377409693858</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="M37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="N37" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="O37" t="n">
         <v>901.5240037917935</v>
@@ -7131,7 +7131,7 @@
         <v>478.6599739669085</v>
       </c>
       <c r="Y37" t="n">
-        <v>482.1592746459644</v>
+        <v>482.1592746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7141,25 +7141,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C38" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D38" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E38" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F38" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G38" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H38" t="n">
-        <v>70.38201150041843</v>
+        <v>61.84</v>
       </c>
       <c r="I38" t="n">
         <v>61.84</v>
@@ -7168,22 +7168,22 @@
         <v>445.5561922637023</v>
       </c>
       <c r="K38" t="n">
-        <v>430.0181114556214</v>
+        <v>549.5142368557207</v>
       </c>
       <c r="L38" t="n">
-        <v>445.6438562352781</v>
+        <v>534.8986329685373</v>
       </c>
       <c r="M38" t="n">
-        <v>951.3269046272115</v>
+        <v>519.3605521604553</v>
       </c>
       <c r="N38" t="n">
-        <v>1561.45999999989</v>
+        <v>1129.493647533134</v>
       </c>
       <c r="O38" t="n">
-        <v>2326.729999999945</v>
+        <v>1894.76364753319</v>
       </c>
       <c r="P38" t="n">
-        <v>3092</v>
+        <v>2660.033647533246</v>
       </c>
       <c r="Q38" t="n">
         <v>3092</v>
@@ -7244,16 +7244,16 @@
         <v>134.974877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>258.9313981428639</v>
+        <v>483.6771006891146</v>
       </c>
       <c r="K39" t="n">
-        <v>448.1242142372473</v>
+        <v>672.869916783498</v>
       </c>
       <c r="L39" t="n">
-        <v>719.4746758324475</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M39" t="n">
-        <v>805.5552175753068</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N39" t="n">
         <v>1163.581204729126</v>
@@ -7329,22 +7329,22 @@
         <v>1011.831843630703</v>
       </c>
       <c r="L40" t="n">
-        <v>1011.831843630703</v>
+        <v>877.945350542037</v>
       </c>
       <c r="M40" t="n">
-        <v>1011.831843630703</v>
+        <v>645.9942279131988</v>
       </c>
       <c r="N40" t="n">
-        <v>1011.831843630703</v>
+        <v>362.9790003660423</v>
       </c>
       <c r="O40" t="n">
-        <v>1011.831843630703</v>
+        <v>61.84</v>
       </c>
       <c r="P40" t="n">
-        <v>611.3794220869881</v>
+        <v>61.84</v>
       </c>
       <c r="Q40" t="n">
-        <v>501.8421494759102</v>
+        <v>61.84</v>
       </c>
       <c r="R40" t="n">
         <v>61.84</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>647.1529471047825</v>
+        <v>697.0151441276475</v>
       </c>
       <c r="C41" t="n">
-        <v>647.1529471047825</v>
+        <v>458.1519337811891</v>
       </c>
       <c r="D41" t="n">
-        <v>447.8204665594797</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="E41" t="n">
-        <v>254.5242144313295</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="F41" t="n">
-        <v>254.5242144313295</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="G41" t="n">
-        <v>61.84</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="H41" t="n">
         <v>61.84</v>
@@ -7402,52 +7402,52 @@
         <v>61.84</v>
       </c>
       <c r="J41" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K41" t="n">
-        <v>764.0617564435721</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L41" t="n">
-        <v>764.0617564435721</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="M41" t="n">
-        <v>1274.910585172507</v>
+        <v>1673.704308114459</v>
       </c>
       <c r="N41" t="n">
-        <v>1888.13090494727</v>
+        <v>2286.924627889222</v>
       </c>
       <c r="O41" t="n">
-        <v>2653.400904947332</v>
+        <v>2326.729999999937</v>
       </c>
       <c r="P41" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="Q41" t="n">
         <v>3092</v>
       </c>
       <c r="R41" t="n">
-        <v>3092</v>
+        <v>3053.738789062329</v>
       </c>
       <c r="S41" t="n">
-        <v>2889.00963807784</v>
+        <v>2769.043670070084</v>
       </c>
       <c r="T41" t="n">
-        <v>2511.559555523735</v>
+        <v>2391.593587515979</v>
       </c>
       <c r="U41" t="n">
-        <v>2070.931983252411</v>
+        <v>1950.966015244655</v>
       </c>
       <c r="V41" t="n">
-        <v>1649.870342679862</v>
+        <v>1529.904374672105</v>
       </c>
       <c r="W41" t="n">
-        <v>1220.200164921329</v>
+        <v>1100.234196913573</v>
       </c>
       <c r="X41" t="n">
-        <v>1220.200164921329</v>
+        <v>717.1212338219889</v>
       </c>
       <c r="Y41" t="n">
-        <v>918.869424837686</v>
+        <v>697.0151441276475</v>
       </c>
     </row>
     <row r="42">
@@ -7481,31 +7481,31 @@
         <v>61.84</v>
       </c>
       <c r="J42" t="n">
-        <v>396.666520175299</v>
+        <v>225.538096574708</v>
       </c>
       <c r="K42" t="n">
-        <v>796.7293362696823</v>
+        <v>625.6009126690915</v>
       </c>
       <c r="L42" t="n">
-        <v>1278.949797864882</v>
+        <v>1107.821374264292</v>
       </c>
       <c r="M42" t="n">
-        <v>1575.900339607742</v>
+        <v>1404.771916007151</v>
       </c>
       <c r="N42" t="n">
-        <v>1866.192460435215</v>
+        <v>1748.922200614719</v>
       </c>
       <c r="O42" t="n">
-        <v>2316.104912118933</v>
+        <v>2198.834652298438</v>
       </c>
       <c r="P42" t="n">
-        <v>2639.50425658844</v>
+        <v>2522.233996767945</v>
       </c>
       <c r="Q42" t="n">
-        <v>2679.025784148865</v>
+        <v>2561.75552432837</v>
       </c>
       <c r="R42" t="n">
-        <v>2480.230476522543</v>
+        <v>2224.105224033037</v>
       </c>
       <c r="S42" t="n">
         <v>2224.105224033037</v>
@@ -7536,22 +7536,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>77.77043040567538</v>
+        <v>134.0655866917276</v>
       </c>
       <c r="C43" t="n">
-        <v>77.77043040567538</v>
+        <v>123.842884815901</v>
       </c>
       <c r="D43" t="n">
-        <v>77.77043040567538</v>
+        <v>123.842884815901</v>
       </c>
       <c r="E43" t="n">
-        <v>77.77043040567538</v>
+        <v>123.842884815901</v>
       </c>
       <c r="F43" t="n">
-        <v>77.77043040567538</v>
+        <v>61.84</v>
       </c>
       <c r="G43" t="n">
-        <v>77.77043040567538</v>
+        <v>61.84</v>
       </c>
       <c r="H43" t="n">
         <v>61.84</v>
@@ -7560,52 +7560,52 @@
         <v>61.84</v>
       </c>
       <c r="J43" t="n">
-        <v>61.84</v>
+        <v>220.3975134648165</v>
       </c>
       <c r="K43" t="n">
-        <v>61.84</v>
+        <v>220.3975134648165</v>
       </c>
       <c r="L43" t="n">
-        <v>61.84</v>
+        <v>220.3975134648165</v>
       </c>
       <c r="M43" t="n">
-        <v>61.84</v>
+        <v>220.3975134648165</v>
       </c>
       <c r="N43" t="n">
-        <v>61.84</v>
+        <v>220.3975134648165</v>
       </c>
       <c r="O43" t="n">
-        <v>61.84</v>
+        <v>220.3975134648165</v>
       </c>
       <c r="P43" t="n">
-        <v>61.84</v>
+        <v>220.3975134648165</v>
       </c>
       <c r="Q43" t="n">
-        <v>61.84</v>
+        <v>220.3975134648165</v>
       </c>
       <c r="R43" t="n">
-        <v>61.84</v>
+        <v>220.3975134648165</v>
       </c>
       <c r="S43" t="n">
-        <v>61.84</v>
+        <v>69.51521073465946</v>
       </c>
       <c r="T43" t="n">
-        <v>61.84</v>
+        <v>72.46088989346433</v>
       </c>
       <c r="U43" t="n">
-        <v>91.27831913164476</v>
+        <v>133.882082531751</v>
       </c>
       <c r="V43" t="n">
-        <v>91.27831913164476</v>
+        <v>147.5734754176969</v>
       </c>
       <c r="W43" t="n">
-        <v>77.77043040567538</v>
+        <v>134.0655866917276</v>
       </c>
       <c r="X43" t="n">
-        <v>77.77043040567538</v>
+        <v>134.0655866917276</v>
       </c>
       <c r="Y43" t="n">
-        <v>77.77043040567538</v>
+        <v>134.0655866917276</v>
       </c>
     </row>
     <row r="44">
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>287.4351068079291</v>
+        <v>61.84</v>
       </c>
       <c r="C44" t="n">
-        <v>287.4351068079291</v>
+        <v>61.84</v>
       </c>
       <c r="D44" t="n">
         <v>61.84</v>
@@ -7654,37 +7654,37 @@
         <v>1577.218261541354</v>
       </c>
       <c r="O44" t="n">
-        <v>2342.488261541431</v>
+        <v>2326.729999999922</v>
       </c>
       <c r="P44" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="Q44" t="n">
         <v>3092</v>
       </c>
       <c r="R44" t="n">
-        <v>3027.476162799703</v>
+        <v>3092</v>
       </c>
       <c r="S44" t="n">
-        <v>3027.476162799703</v>
+        <v>2781.042254745129</v>
       </c>
       <c r="T44" t="n">
-        <v>2623.763453982971</v>
+        <v>2377.329545928397</v>
       </c>
       <c r="U44" t="n">
-        <v>2156.873255449021</v>
+        <v>1910.439347394447</v>
       </c>
       <c r="V44" t="n">
-        <v>1709.548988613845</v>
+        <v>1463.115080559271</v>
       </c>
       <c r="W44" t="n">
-        <v>1253.616184592686</v>
+        <v>1007.182276538112</v>
       </c>
       <c r="X44" t="n">
-        <v>844.2405952384764</v>
+        <v>687.412470341799</v>
       </c>
       <c r="Y44" t="n">
-        <v>585.4142108034589</v>
+        <v>359.8191039955299</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1028.890452379605</v>
+        <v>579.551755451169</v>
       </c>
       <c r="C45" t="n">
-        <v>853.031954959888</v>
+        <v>403.6932580314526</v>
       </c>
       <c r="D45" t="n">
-        <v>690.4686348611986</v>
+        <v>403.6932580314526</v>
       </c>
       <c r="E45" t="n">
-        <v>533.2240922128019</v>
+        <v>246.448715383056</v>
       </c>
       <c r="F45" t="n">
-        <v>379.04606964929</v>
+        <v>92.27069281954398</v>
       </c>
       <c r="G45" t="n">
-        <v>238.9051243209795</v>
+        <v>92.27069281954398</v>
       </c>
       <c r="H45" t="n">
         <v>92.27069281954398</v>
@@ -7721,49 +7721,49 @@
         <v>370.9265201752989</v>
       </c>
       <c r="K45" t="n">
-        <v>578.9400186606695</v>
+        <v>745.2493362696823</v>
       </c>
       <c r="L45" t="n">
-        <v>1035.42048025587</v>
+        <v>1201.729797864882</v>
       </c>
       <c r="M45" t="n">
-        <v>1306.631021998729</v>
+        <v>1344.295411824231</v>
       </c>
       <c r="N45" t="n">
-        <v>1625.041306606297</v>
+        <v>1662.705696431799</v>
       </c>
       <c r="O45" t="n">
-        <v>2049.213758290016</v>
+        <v>2086.878148115518</v>
       </c>
       <c r="P45" t="n">
-        <v>2346.873102759523</v>
+        <v>2384.537492585025</v>
       </c>
       <c r="Q45" t="n">
-        <v>2360.654630319948</v>
+        <v>2384.537492585025</v>
       </c>
       <c r="R45" t="n">
-        <v>2343.930332204927</v>
+        <v>2020.624566027066</v>
       </c>
       <c r="S45" t="n">
-        <v>2343.930332204927</v>
+        <v>1894.591635276492</v>
       </c>
       <c r="T45" t="n">
-        <v>2123.366932995317</v>
+        <v>1674.028236066882</v>
       </c>
       <c r="U45" t="n">
-        <v>1908.002933237553</v>
+        <v>1458.664236309117</v>
       </c>
       <c r="V45" t="n">
-        <v>1678.194178498644</v>
+        <v>1228.855481570208</v>
       </c>
       <c r="W45" t="n">
-        <v>1678.194178498644</v>
+        <v>1228.855481570208</v>
       </c>
       <c r="X45" t="n">
-        <v>1442.979290169969</v>
+        <v>993.6405932415337</v>
       </c>
       <c r="Y45" t="n">
-        <v>1228.442529800137</v>
+        <v>779.103832871701</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="C46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="D46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="E46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="F46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="G46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="H46" t="n">
         <v>61.84</v>
       </c>
       <c r="I46" t="n">
-        <v>72.10287893608292</v>
+        <v>61.84</v>
       </c>
       <c r="J46" t="n">
-        <v>143.672759546362</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="K46" t="n">
-        <v>143.672759546362</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="L46" t="n">
-        <v>143.672759546362</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="M46" t="n">
-        <v>143.672759546362</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="N46" t="n">
-        <v>143.672759546362</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="O46" t="n">
-        <v>143.672759546362</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="P46" t="n">
-        <v>143.672759546362</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="Q46" t="n">
-        <v>143.672759546362</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="R46" t="n">
-        <v>143.672759546362</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="S46" t="n">
-        <v>143.672759546362</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="T46" t="n">
-        <v>120.4156216612533</v>
+        <v>113.9037576312383</v>
       </c>
       <c r="U46" t="n">
-        <v>156.0968142995399</v>
+        <v>113.9037576312383</v>
       </c>
       <c r="V46" t="n">
-        <v>143.8035716568973</v>
+        <v>101.6105149885956</v>
       </c>
       <c r="W46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="X46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="Y46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
     </row>
   </sheetData>
@@ -7964,13 +7964,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>814.0000000000001</v>
+        <v>299.9792987747927</v>
       </c>
       <c r="M2" t="n">
         <v>544.2621276423173</v>
@@ -7979,13 +7979,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
-        <v>362.12108763204</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q2" t="n">
-        <v>189.0212843274853</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>51.24160624509022</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M5" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>884.2478695740924</v>
+        <v>175.641632767838</v>
       </c>
       <c r="P5" t="n">
         <v>814.2870600406815</v>
       </c>
       <c r="Q5" t="n">
-        <v>480.8945023854328</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,25 +8441,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>500.8454983898731</v>
+        <v>532.2245521358337</v>
       </c>
       <c r="M8" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O8" t="n">
         <v>884.2478695740924</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2870600406860149</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q8" t="n">
-        <v>615.8520732695737</v>
+        <v>189.0212843274853</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,16 +8675,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>814.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1060.271045550332</v>
+        <v>778.7925375282215</v>
       </c>
       <c r="N11" t="n">
         <v>1096.663422488788</v>
@@ -8693,7 +8693,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
-        <v>114.0702823596368</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8921,13 +8921,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1060.271045550332</v>
+        <v>681.6676550513207</v>
       </c>
       <c r="N14" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>505.6444790750808</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P14" t="n">
         <v>814.2870600406815</v>
@@ -9155,22 +9155,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>517.1938323746919</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>884.2478695740924</v>
+        <v>231.79875049407</v>
       </c>
       <c r="P17" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,22 +9386,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>240.8110739199409</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N20" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
-        <v>884.2478695740924</v>
+        <v>505.4544742200154</v>
       </c>
       <c r="P20" t="n">
         <v>814.2870600406815</v>
@@ -9626,19 +9626,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>240.8110739199409</v>
+        <v>814</v>
       </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N23" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O23" t="n">
-        <v>884.2478695740924</v>
+        <v>110.1927438789493</v>
       </c>
       <c r="P23" t="n">
         <v>814.2870600406815</v>
@@ -9863,25 +9863,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>772.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>693.841480123215</v>
       </c>
       <c r="O26" t="n">
-        <v>673.7448980926609</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>773.2870600407081</v>
+        <v>773.287060040709</v>
       </c>
       <c r="Q26" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10109,13 +10109,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>1096.663422488788</v>
+        <v>1080.745986588361</v>
       </c>
       <c r="O29" t="n">
-        <v>843.2478695741263</v>
+        <v>843.2478695741272</v>
       </c>
       <c r="P29" t="n">
-        <v>757.3696241402899</v>
+        <v>773.2870600407163</v>
       </c>
       <c r="Q29" t="n">
         <v>172.8226843274854</v>
@@ -10334,25 +10334,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>80.27785409340875</v>
       </c>
       <c r="K32" t="n">
-        <v>221.706710657067</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1060.271045550332</v>
+        <v>1012.590174281196</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>843.2478695741336</v>
+        <v>843.2478695741345</v>
       </c>
       <c r="P32" t="n">
-        <v>773.2870600407226</v>
+        <v>773.2870600407235</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10571,13 +10571,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>50.42570624509131</v>
       </c>
       <c r="K35" t="n">
-        <v>14.5562351802393</v>
+        <v>455.710033445301</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>727.1079320759981</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
@@ -10586,10 +10586,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>843.2478695741409</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>15.6697600406826</v>
+        <v>773.2870600407308</v>
       </c>
       <c r="Q35" t="n">
         <v>188.2053843274865</v>
@@ -10811,25 +10811,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>118.3011641460982</v>
       </c>
       <c r="L38" t="n">
-        <v>29.93893518017202</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>843.2478695741481</v>
+        <v>843.247869574149</v>
       </c>
       <c r="P38" t="n">
-        <v>773.2870600407372</v>
+        <v>773.2870600407381</v>
       </c>
       <c r="Q38" t="n">
-        <v>188.2053843274866</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,10 +11045,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>709.3149054985578</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11060,13 +11060,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>843.2478695741554</v>
+        <v>110.4553161505717</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407454</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11297,13 +11297,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>843.24786957417</v>
+        <v>827.3304336736564</v>
       </c>
       <c r="P44" t="n">
-        <v>314.3402351981579</v>
+        <v>773.2870600407599</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22706,7 +22706,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>29.21007785422719</v>
+        <v>29.21007785422989</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5.662449696445705</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>5.662449696444753</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>5.66244969644525</v>
+        <v>5.662449696446828</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23226,19 +23226,19 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>58.95976110113358</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>128.7099412994061</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23289,10 +23289,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -23423,13 +23423,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23472,10 +23472,10 @@
         <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>86.30994672070055</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>152.7573722870162</v>
+        <v>85.17769029970491</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23663,13 +23663,13 @@
         <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>421.860847251041</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>111.3734797028554</v>
+        <v>58.39506052829842</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4306086145859922</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23864,7 +23864,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -23882,16 +23882,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>361.445564079015</v>
@@ -23900,13 +23900,13 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>206.2239967202628</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>10.11394863308971</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23924,7 +23924,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -24092,16 +24092,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1.98090483695654</v>
+        <v>0.5931748319466539</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -24122,28 +24122,28 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L22" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>69.04626797189979</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R22" t="n">
         <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -24359,25 +24359,25 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>253.5689831290532</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
         <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>446.839266425598</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24408,25 +24408,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23.5808252291871</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>35.06290239760591</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,10 +24459,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>361.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -24575,13 +24575,13 @@
         <v>60.53621805555548</v>
       </c>
       <c r="E28" t="n">
-        <v>33.27936218108634</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>49.38285596774193</v>
       </c>
       <c r="G28" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -24599,10 +24599,10 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>346.1850752716849</v>
+        <v>218.8065331644993</v>
       </c>
       <c r="O28" t="n">
         <v>415.445564079015</v>
@@ -24617,7 +24617,7 @@
         <v>501.6021279811511</v>
       </c>
       <c r="S28" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24632,7 +24632,7 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y28" t="n">
         <v>62.46535284946236</v>
@@ -24648,22 +24648,22 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>35.06290239760591</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>178.7573722870162</v>
+        <v>103.8272349133216</v>
       </c>
       <c r="H29" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24702,13 +24702,13 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -24821,7 +24821,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24836,7 +24836,7 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>346.1850752716849</v>
@@ -24851,7 +24851,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -24872,7 +24872,7 @@
         <v>22.44364543010755</v>
       </c>
       <c r="Y31" t="n">
-        <v>62.46535284946236</v>
+        <v>13.54903866186601</v>
       </c>
     </row>
     <row r="32">
@@ -25070,28 +25070,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>85.5866114845816</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q34" t="n">
         <v>434.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>435.6021279811511</v>
+        <v>208.8479973216012</v>
       </c>
       <c r="S34" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25316,7 +25316,7 @@
         <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>240.2408026384713</v>
+        <v>240.2408026384947</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -25544,25 +25544,25 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>349.445564079015</v>
+        <v>51.3179537166331</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>326.3973665406309</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S40" t="n">
         <v>71.37347970285543</v>
@@ -25593,25 +25593,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>236.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>191.3632896068686</v>
       </c>
       <c r="F41" t="n">
         <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>195.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,10 +25641,10 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>37.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>80.88770949938453</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -25659,10 +25659,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>379.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>278.4124038854085</v>
       </c>
     </row>
     <row r="42">
@@ -25720,10 +25720,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>137.4664427423205</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>253.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25754,7 +25754,7 @@
         <v>74.11380033707866</v>
       </c>
       <c r="C43" t="n">
-        <v>59.72524664804467</v>
+        <v>49.60477179097634</v>
       </c>
       <c r="D43" t="n">
         <v>72.53621805555548</v>
@@ -25763,13 +25763,13 @@
         <v>67.98090483695654</v>
       </c>
       <c r="F43" t="n">
-        <v>61.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>32.04387284153003</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>15.77112610161862</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>513.6021279811511</v>
       </c>
       <c r="S43" t="n">
-        <v>149.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25836,7 +25836,7 @@
         <v>262.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>217.3632896068686</v>
@@ -25878,10 +25878,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
-        <v>307.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -25896,10 +25896,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>88.70972532631777</v>
       </c>
       <c r="Y44" t="n">
-        <v>68.07931209213905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -25915,7 +25915,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>160.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -25924,10 +25924,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>138.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>145.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25957,10 +25957,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>343.7167421585088</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>279.5639999646113</v>
+        <v>154.791398521543</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -26006,7 +26006,7 @@
         <v>58.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>41.77112610161862</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4582157.628270562</v>
+        <v>4582157.628270563</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5222214.524375137</v>
+        <v>5222214.524375139</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5803822.866577105</v>
+        <v>5803822.866577106</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6388338.779688163</v>
+        <v>6388338.779688164</v>
       </c>
     </row>
     <row r="12">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>7676764.029526547</v>
+        <v>7676764.029526548</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8320428.258564216</v>
+        <v>8320428.258564218</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>8886400.989223231</v>
+        <v>8886400.989223229</v>
       </c>
     </row>
     <row r="16">
@@ -26281,7 +26281,7 @@
         <v>1379385.55305381</v>
       </c>
       <c r="F2" t="n">
-        <v>1435639.178444159</v>
+        <v>1435639.17844416</v>
       </c>
       <c r="G2" t="n">
         <v>1493466.090910675</v>
@@ -26290,10 +26290,10 @@
         <v>1493466.09091068</v>
       </c>
       <c r="I2" t="n">
-        <v>1493466.090910681</v>
+        <v>1493466.090910682</v>
       </c>
       <c r="J2" t="n">
-        <v>1363870.463925811</v>
+        <v>1363870.46392581</v>
       </c>
       <c r="K2" t="n">
         <v>1363870.463925811</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>556224.196455833</v>
+        <v>551386.5909530218</v>
       </c>
       <c r="C4" t="n">
-        <v>554472.2877165735</v>
+        <v>549634.6822137623</v>
       </c>
       <c r="D4" t="n">
-        <v>552718.0024037627</v>
+        <v>547880.3969009516</v>
       </c>
       <c r="E4" t="n">
-        <v>474694.9568742209</v>
+        <v>469906.9358754652</v>
       </c>
       <c r="F4" t="n">
-        <v>498969.5726682167</v>
+        <v>494181.5516694608</v>
       </c>
       <c r="G4" t="n">
-        <v>523758.9807925398</v>
+        <v>518970.9597937841</v>
       </c>
       <c r="H4" t="n">
-        <v>522086.045852445</v>
+        <v>517298.0248536893</v>
       </c>
       <c r="I4" t="n">
-        <v>520410.775468019</v>
+        <v>515622.7544692633</v>
       </c>
       <c r="J4" t="n">
-        <v>464369.6125335261</v>
+        <v>459704.5839768919</v>
       </c>
       <c r="K4" t="n">
-        <v>462904.8708795845</v>
+        <v>458239.8423229501</v>
       </c>
       <c r="L4" t="n">
-        <v>524533.914492766</v>
+        <v>519822.4908174388</v>
       </c>
       <c r="M4" t="n">
-        <v>522803.7957912139</v>
+        <v>518092.3721158857</v>
       </c>
       <c r="N4" t="n">
-        <v>521071.1894666612</v>
+        <v>516359.7657913335</v>
       </c>
       <c r="O4" t="n">
-        <v>438916.084163369</v>
+        <v>434251.0556067348</v>
       </c>
       <c r="P4" t="n">
-        <v>398110.3467682331</v>
+        <v>393445.3182115989</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>616007.1016626814</v>
+        <v>620844.7071654929</v>
       </c>
       <c r="C6" t="n">
-        <v>904287.0104019411</v>
+        <v>909124.6159047526</v>
       </c>
       <c r="D6" t="n">
-        <v>906041.2957147523</v>
+        <v>910878.9012175633</v>
       </c>
       <c r="E6" t="n">
-        <v>656283.8711795897</v>
+        <v>661071.8921783454</v>
       </c>
       <c r="F6" t="n">
-        <v>845277.0867759424</v>
+        <v>850065.1077746991</v>
       </c>
       <c r="G6" t="n">
-        <v>874360.659118135</v>
+        <v>879148.6801168905</v>
       </c>
       <c r="H6" t="n">
-        <v>898433.5940582351</v>
+        <v>903221.6150569908</v>
       </c>
       <c r="I6" t="n">
-        <v>900108.8644426623</v>
+        <v>904896.8854414185</v>
       </c>
       <c r="J6" t="n">
-        <v>424690.9263922844</v>
+        <v>429355.9549489182</v>
       </c>
       <c r="K6" t="n">
-        <v>814251.668046226</v>
+        <v>818916.6966028607</v>
       </c>
       <c r="L6" t="n">
-        <v>830686.8075951207</v>
+        <v>835398.2312704485</v>
       </c>
       <c r="M6" t="n">
-        <v>907616.9262966735</v>
+        <v>912328.3499720015</v>
       </c>
       <c r="N6" t="n">
-        <v>909349.532621226</v>
+        <v>914060.9562965536</v>
       </c>
       <c r="O6" t="n">
-        <v>744941.0378214428</v>
+        <v>749606.0663780768</v>
       </c>
       <c r="P6" t="n">
-        <v>773330.9934640047</v>
+        <v>777996.0220206392</v>
       </c>
     </row>
   </sheetData>
@@ -27005,7 +27005,7 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27024,10 +27024,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>-0</v>
@@ -27045,19 +27045,19 @@
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>-0</v>
@@ -27433,13 +27433,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>400</v>
@@ -27451,10 +27451,10 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,16 +27481,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>157.3092074428799</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U2" t="n">
-        <v>307.3903671255646</v>
+        <v>400</v>
       </c>
       <c r="V2" t="n">
         <v>400</v>
@@ -27499,7 +27499,7 @@
         <v>400</v>
       </c>
       <c r="X2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>400</v>
@@ -27512,25 +27512,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>172.5204020740698</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>198.6352617872018</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -27594,25 +27594,25 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>379.0511466643184</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
+        <v>228.7711261016186</v>
+      </c>
+      <c r="I4" t="n">
         <v>400</v>
-      </c>
-      <c r="I4" t="n">
-        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
@@ -27645,13 +27645,13 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>355.4483345055817</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
@@ -27660,7 +27660,7 @@
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27676,7 +27676,7 @@
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>400</v>
@@ -27685,46 +27685,46 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
+        <v>56.51176829727024</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>250.8785988282945</v>
+      </c>
+      <c r="S5" t="n">
         <v>400</v>
       </c>
-      <c r="H5" t="n">
-        <v>307.3903671255651</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -27767,7 +27767,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27797,19 +27797,19 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
       </c>
       <c r="T6" t="n">
+        <v>274.4424628029984</v>
+      </c>
+      <c r="U6" t="n">
         <v>400</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
-        <v>342.2743756165772</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27831,10 +27831,10 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
@@ -27846,7 +27846,7 @@
         <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>260.3059756611662</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
@@ -27855,7 +27855,7 @@
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>361.3978336293952</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,22 +27882,22 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56.51176829726984</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27916,16 +27916,16 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>400</v>
+        <v>56.51176829727029</v>
       </c>
       <c r="F8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27961,13 +27961,13 @@
         <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
@@ -27989,13 +27989,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>193.9840721817118</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28031,16 +28031,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>115.3536407070569</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>370.8820140359639</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28083,10 +28083,10 @@
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>395.1184894125584</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
         <v>210.0245665062577</v>
@@ -28125,16 +28125,16 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W10" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X10" t="n">
         <v>400</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>400</v>
-      </c>
-      <c r="X10" t="n">
-        <v>247.4436454301076</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28253,7 +28253,7 @@
         <v>225</v>
       </c>
       <c r="L12" t="n">
-        <v>225</v>
+        <v>19.1168712588389</v>
       </c>
       <c r="M12" t="n">
         <v>225</v>
@@ -28262,7 +28262,7 @@
         <v>225</v>
       </c>
       <c r="O12" t="n">
-        <v>19.11687125883876</v>
+        <v>225</v>
       </c>
       <c r="P12" t="n">
         <v>225</v>
@@ -28484,25 +28484,25 @@
         <v>251</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="M15" t="n">
-        <v>166.1982915220776</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>251</v>
+        <v>166.1982915220777</v>
       </c>
       <c r="Q15" t="n">
         <v>251</v>
@@ -28718,31 +28718,31 @@
         <v>279</v>
       </c>
       <c r="I18" t="n">
+        <v>261.5913251766235</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>279</v>
-      </c>
-      <c r="J18" t="n">
-        <v>155.6705902671031</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>279</v>
       </c>
       <c r="Q18" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28958,28 +28958,28 @@
         <v>279</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>279</v>
       </c>
-      <c r="K21" t="n">
-        <v>155.6705902671031</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>261.5913251766236</v>
       </c>
       <c r="Q21" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
         <v>279</v>
@@ -29195,25 +29195,25 @@
         <v>279</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>279</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>155.6705902671032</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>155.6705902671034</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>279</v>
@@ -29429,7 +29429,7 @@
         <v>225</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J27" t="n">
         <v>225</v>
@@ -29447,7 +29447,7 @@
         <v>225</v>
       </c>
       <c r="O27" t="n">
-        <v>26.99048536749061</v>
+        <v>19.11687125883898</v>
       </c>
       <c r="P27" t="n">
         <v>225</v>
@@ -29860,7 +29860,7 @@
         <v>291</v>
       </c>
       <c r="U32" t="n">
-        <v>291</v>
+        <v>282.5434086145858</v>
       </c>
       <c r="V32" t="n">
         <v>291</v>
@@ -29872,7 +29872,7 @@
         <v>291</v>
       </c>
       <c r="Y32" t="n">
-        <v>282.5434086145857</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33">
@@ -29906,13 +29906,13 @@
         <v>291</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>53.93659606734957</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -29924,10 +29924,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>227.0158611578289</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
         <v>291</v>
@@ -30030,7 +30030,7 @@
         <v>291</v>
       </c>
       <c r="Y34" t="n">
-        <v>291</v>
+        <v>291.0000000000239</v>
       </c>
     </row>
     <row r="35">
@@ -30061,7 +30061,7 @@
         <v>291</v>
       </c>
       <c r="I35" t="n">
-        <v>141.6245682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
-        <v>291</v>
+        <v>282.5434086145851</v>
       </c>
       <c r="T35" t="n">
         <v>291</v>
@@ -30140,25 +30140,25 @@
         <v>291</v>
       </c>
       <c r="I36" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>9.889475266480218</v>
+      </c>
+      <c r="O36" t="n">
         <v>291</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>227.0158611578289</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -30267,7 +30267,7 @@
         <v>291</v>
       </c>
       <c r="Y37" t="n">
-        <v>291.0000000000239</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38">
@@ -30277,7 +30277,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>291</v>
+        <v>282.5434086145858</v>
       </c>
       <c r="C38" t="n">
         <v>291</v>
@@ -30298,7 +30298,7 @@
         <v>291</v>
       </c>
       <c r="I38" t="n">
-        <v>141.6245682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30380,7 +30380,7 @@
         <v>291</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>227.015861157829</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -30392,7 +30392,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>227.0158611578289</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -30617,7 +30617,7 @@
         <v>213</v>
       </c>
       <c r="J42" t="n">
-        <v>213</v>
+        <v>40.14300646404961</v>
       </c>
       <c r="K42" t="n">
         <v>213</v>
@@ -30629,7 +30629,7 @@
         <v>213</v>
       </c>
       <c r="N42" t="n">
-        <v>158.5978143635403</v>
+        <v>213</v>
       </c>
       <c r="O42" t="n">
         <v>213</v>
@@ -30696,7 +30696,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>35.26894883590776</v>
+        <v>195.4280533458234</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30726,13 +30726,13 @@
         <v>213</v>
       </c>
       <c r="T43" t="n">
-        <v>210.0245665062577</v>
+        <v>213</v>
       </c>
       <c r="U43" t="n">
-        <v>180.6940671650082</v>
+        <v>213</v>
       </c>
       <c r="V43" t="n">
-        <v>199.1703102162162</v>
+        <v>213</v>
       </c>
       <c r="W43" t="n">
         <v>213</v>
@@ -30857,13 +30857,13 @@
         <v>187</v>
       </c>
       <c r="K45" t="n">
-        <v>19.01079029392637</v>
+        <v>187</v>
       </c>
       <c r="L45" t="n">
         <v>187</v>
       </c>
       <c r="M45" t="n">
-        <v>187</v>
+        <v>57.05562850150396</v>
       </c>
       <c r="N45" t="n">
         <v>187</v>
@@ -30875,7 +30875,7 @@
         <v>187</v>
       </c>
       <c r="Q45" t="n">
-        <v>187</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
         <v>187</v>
@@ -30930,10 +30930,10 @@
         <v>187</v>
       </c>
       <c r="I46" t="n">
-        <v>187</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J46" t="n">
-        <v>107.5617575331594</v>
+        <v>111.3506614786826</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -30966,7 +30966,7 @@
         <v>187</v>
       </c>
       <c r="U46" t="n">
-        <v>187</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V46" t="n">
         <v>187</v>
@@ -34749,7 +34749,7 @@
         <v>814.0000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M2" t="n">
         <v>814</v>
@@ -34880,25 +34880,25 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>106.3259000162737</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -34931,13 +34931,13 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>156.2780242893655</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
@@ -34946,7 +34946,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34983,10 +34983,10 @@
         <v>814</v>
       </c>
       <c r="K5" t="n">
+        <v>814.0000000000001</v>
+      </c>
+      <c r="L5" t="n">
         <v>814</v>
-      </c>
-      <c r="L5" t="n">
-        <v>814.0000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>814</v>
@@ -35117,10 +35117,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
@@ -35132,7 +35132,7 @@
         <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>31.53484955954758</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
         <v>223.3665443798817</v>
@@ -35141,7 +35141,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>72.87705982825213</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35168,22 +35168,22 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
         <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35220,7 +35220,7 @@
         <v>814</v>
       </c>
       <c r="K8" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
@@ -35235,7 +35235,7 @@
         <v>814</v>
       </c>
       <c r="P8" t="n">
-        <v>814.0000000000045</v>
+        <v>814</v>
       </c>
       <c r="Q8" t="n">
         <v>814</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>83.76821369888529</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35369,10 +35369,10 @@
         <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>218.4850337924401</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -35411,16 +35411,16 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,16 +35454,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L11" t="n">
-        <v>814.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>516.0089179080152</v>
+        <v>234.5304098859042</v>
       </c>
       <c r="N11" t="n">
         <v>619.4144644189528</v>
@@ -35472,7 +35472,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>113.7832223189554</v>
+        <v>814</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35539,7 +35539,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>499.091375348687</v>
+        <v>293.2082466075259</v>
       </c>
       <c r="M12" t="n">
         <v>311.9500421645043</v>
@@ -35548,7 +35548,7 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O12" t="n">
-        <v>260.5738931615851</v>
+        <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
         <v>338.6660045146532</v>
@@ -35700,13 +35700,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>516.0089179080152</v>
+        <v>137.4055274090034</v>
       </c>
       <c r="N14" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>435.3966095009883</v>
+        <v>814</v>
       </c>
       <c r="P14" t="n">
         <v>814</v>
@@ -35770,25 +35770,25 @@
         <v>33.87361410865147</v>
       </c>
       <c r="J15" t="n">
-        <v>125.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>191.1038546407913</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>274.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M15" t="n">
-        <v>253.1483336865819</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N15" t="n">
-        <v>385.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>492.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>364.6660045146532</v>
+        <v>279.8642960367309</v>
       </c>
       <c r="Q15" t="n">
         <v>77.92073490952041</v>
@@ -35934,22 +35934,22 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>39.94487430485665</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>814</v>
+        <v>161.5508809199775</v>
       </c>
       <c r="P17" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36004,10 +36004,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>61.87361410865147</v>
+        <v>44.46493928527492</v>
       </c>
       <c r="J18" t="n">
-        <v>280.8791965047788</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
         <v>191.1038546407913</v>
@@ -36022,13 +36022,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P18" t="n">
         <v>392.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36165,22 +36165,22 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>240.8110739199409</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>814</v>
+        <v>435.2066046459229</v>
       </c>
       <c r="P20" t="n">
         <v>814</v>
@@ -36244,10 +36244,10 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J21" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>346.7744449078945</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
         <v>274.091375348687</v>
@@ -36259,13 +36259,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>113.6660045146532</v>
+        <v>375.2573296912768</v>
       </c>
       <c r="Q21" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36405,19 +36405,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L23" t="n">
-        <v>240.8110739199409</v>
+        <v>814</v>
       </c>
       <c r="M23" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>814</v>
+        <v>39.94487430485688</v>
       </c>
       <c r="P23" t="n">
         <v>814</v>
@@ -36481,7 +36481,7 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J24" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
         <v>191.1038546407913</v>
@@ -36490,16 +36490,16 @@
         <v>274.091375348687</v>
       </c>
       <c r="M24" t="n">
-        <v>86.95004216450428</v>
+        <v>365.9500421645043</v>
       </c>
       <c r="N24" t="n">
-        <v>134.6265501086548</v>
+        <v>290.297140375758</v>
       </c>
       <c r="O24" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>269.3365947817566</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q24" t="n">
         <v>105.9207349095204</v>
@@ -36642,25 +36642,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>772.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>216.5925220533797</v>
       </c>
       <c r="O26" t="n">
-        <v>603.4970285185684</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>773.0000000000266</v>
+        <v>773.0000000000275</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36715,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J27" t="n">
         <v>350.2086062376757</v>
@@ -36733,7 +36733,7 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O27" t="n">
-        <v>268.4475072702369</v>
+        <v>260.5738931615854</v>
       </c>
       <c r="P27" t="n">
         <v>338.6660045146532</v>
@@ -36888,13 +36888,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>619.4144644189528</v>
+        <v>603.4970285185254</v>
       </c>
       <c r="O29" t="n">
-        <v>773.0000000000339</v>
+        <v>773.0000000000348</v>
       </c>
       <c r="P29" t="n">
-        <v>757.0825640996085</v>
+        <v>773.0000000000348</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320760617</v>
+        <v>727.1079320762492</v>
       </c>
       <c r="L32" t="n">
         <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="O32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="Q32" t="n">
-        <v>773.0000000000412</v>
+        <v>773.0000000000421</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37192,13 +37192,13 @@
         <v>73.87361410865147</v>
       </c>
       <c r="J33" t="n">
-        <v>125.2086062376757</v>
+        <v>416.2086062376757</v>
       </c>
       <c r="K33" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>274.091375348687</v>
+        <v>328.0279714160366</v>
       </c>
       <c r="M33" t="n">
         <v>86.95004216450428</v>
@@ -37210,10 +37210,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>404.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>53.9365960673493</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37316,7 +37316,7 @@
         <v>43.55635456989245</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.534647150537637</v>
+        <v>3.534647150561582</v>
       </c>
     </row>
     <row r="35">
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320762799</v>
+        <v>773</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>727.1079320759981</v>
       </c>
       <c r="M35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="P35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="Q35" t="n">
-        <v>773.0000000000484</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37426,13 +37426,13 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>73.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K36" t="n">
-        <v>418.1197157986202</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L36" t="n">
         <v>274.091375348687</v>
@@ -37441,10 +37441,10 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N36" t="n">
-        <v>134.6265501086548</v>
+        <v>144.516025375135</v>
       </c>
       <c r="O36" t="n">
-        <v>241.4570219027464</v>
+        <v>532.4570219027464</v>
       </c>
       <c r="P36" t="n">
         <v>113.6660045146532</v>
@@ -37553,7 +37553,7 @@
         <v>43.55635456989245</v>
       </c>
       <c r="Y37" t="n">
-        <v>3.534647150561582</v>
+        <v>3.534647150537637</v>
       </c>
     </row>
     <row r="38">
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="K38" t="n">
         <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>727.1079320759699</v>
+        <v>727.1079320759511</v>
       </c>
       <c r="M38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="N38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="P38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="Q38" t="n">
-        <v>773.0000000000557</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37666,7 +37666,7 @@
         <v>73.87361410865147</v>
       </c>
       <c r="J39" t="n">
-        <v>125.2086062376757</v>
+        <v>352.2244673955047</v>
       </c>
       <c r="K39" t="n">
         <v>191.1038546407913</v>
@@ -37678,7 +37678,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N39" t="n">
-        <v>361.6424112664837</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O39" t="n">
         <v>241.4570219027464</v>
@@ -37824,10 +37824,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>709.3149054985578</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -37839,13 +37839,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>773.000000000063</v>
+        <v>40.20744657647921</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>773.0000000000639</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,7 +37903,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>338.2086062376757</v>
+        <v>165.3516127017253</v>
       </c>
       <c r="K42" t="n">
         <v>404.1038546407913</v>
@@ -37915,7 +37915,7 @@
         <v>299.9500421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>293.2243644721951</v>
+        <v>347.6265501086548</v>
       </c>
       <c r="O42" t="n">
         <v>454.4570219027464</v>
@@ -37982,7 +37982,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>160.1591045099156</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38012,13 +38012,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.975433493742287</v>
       </c>
       <c r="U43" t="n">
-        <v>29.73567589055027</v>
+        <v>62.04160872554206</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>13.82968978378381</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -38076,13 +38076,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>773.0000000000775</v>
+        <v>757.0825640995639</v>
       </c>
       <c r="P44" t="n">
-        <v>314.0531751574765</v>
+        <v>773.0000000000784</v>
       </c>
       <c r="Q44" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38143,13 +38143,13 @@
         <v>312.2086062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>210.1146449347177</v>
+        <v>378.1038546407913</v>
       </c>
       <c r="L45" t="n">
         <v>461.091375348687</v>
       </c>
       <c r="M45" t="n">
-        <v>273.9500421645043</v>
+        <v>144.0056706660083</v>
       </c>
       <c r="N45" t="n">
         <v>321.6265501086548</v>
@@ -38161,7 +38161,7 @@
         <v>300.6660045146532</v>
       </c>
       <c r="Q45" t="n">
-        <v>13.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -38216,10 +38216,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>10.36654437988173</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>72.29280869725164</v>
+        <v>76.08171264277482</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>36.04160872554206</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
